--- a/zwt-finance-system/backend/app/assets/templates/WHT-Template.xlsx
+++ b/zwt-finance-system/backend/app/assets/templates/WHT-Template.xlsx
@@ -263,7 +263,7 @@
     <t>(ข) เงินปันผล ส่วนแบ่งของกำไร ฯลฯ ตามมาตรา 40 (4) (ข)</t>
   </si>
   <si>
-    <t>(1) กรณีผู้ด้รับเงินปันผลได้รับเครดิตภาษี โดยจ่ายจาก</t>
+    <t>(1) กรณีผู้ได้รับเงินปันผลได้รับเครดิตภาษี โดยจ่ายจาก</t>
   </si>
   <si>
     <t>กำไรสุทธิของกิจการที่ต้องเสียภาษีเงินได้นิติบุคคลในอัตราดังนี้</t>
@@ -779,13 +779,6 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color indexed="30"/>
-      <name val="Leelawadee"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
       <color indexed="53"/>
       <name val="Leelawadee"/>
       <charset val="134"/>
@@ -794,6 +787,13 @@
       <b/>
       <sz val="10"/>
       <color indexed="36"/>
+      <name val="Leelawadee"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color indexed="30"/>
       <name val="Leelawadee"/>
       <charset val="134"/>
     </font>
